--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>13</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>117</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>2.081206729911041</v>
       </c>
@@ -1702,9 +1696,6 @@
       <c r="O7" t="n">
         <v>19</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.3361054069011462</v>
       </c>
@@ -2347,7 +2338,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2494,9 +2485,6 @@
       <c r="O11" t="n">
         <v>17</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1588629672808169</v>
       </c>
@@ -3038,9 +3026,6 @@
       <c r="O14" t="n">
         <v>12</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3431,9 +3416,6 @@
       <c r="O16" t="n">
         <v>47</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.8360403103061447</v>
       </c>
@@ -3827,9 +3809,6 @@
       <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -4472,7 +4451,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4619,9 +4598,6 @@
       <c r="O22" t="n">
         <v>7</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -5163,9 +5139,6 @@
       <c r="O25" t="n">
         <v>13</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5556,9 +5529,6 @@
       <c r="O27" t="n">
         <v>36</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.6403713015110895</v>
       </c>
@@ -5952,9 +5922,6 @@
       <c r="O29" t="n">
         <v>8</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -6597,7 +6564,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6744,9 +6711,6 @@
       <c r="O33" t="n">
         <v>20</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1868976085656669</v>
       </c>
@@ -7140,9 +7104,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7288,9 +7249,6 @@
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7681,9 +7639,6 @@
       <c r="O38" t="n">
         <v>39</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.6937355766370136</v>
       </c>
@@ -8077,9 +8032,6 @@
       <c r="O40" t="n">
         <v>4</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -8473,9 +8425,6 @@
       <c r="O42" t="n">
         <v>64</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.210406698541971</v>
       </c>
@@ -8722,7 +8671,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8869,9 +8818,6 @@
       <c r="O44" t="n">
         <v>18</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1682078477091002</v>
       </c>
@@ -9265,9 +9211,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9413,9 +9356,6 @@
       <c r="O47" t="n">
         <v>16</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9806,9 +9746,6 @@
       <c r="O49" t="n">
         <v>39</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.6937355766370136</v>
       </c>
@@ -10202,9 +10139,6 @@
       <c r="O51" t="n">
         <v>9</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -10598,9 +10532,6 @@
       <c r="O53" t="n">
         <v>84</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.588658791836336</v>
       </c>
@@ -10847,7 +10778,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10994,9 +10925,6 @@
       <c r="O55" t="n">
         <v>26</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.242966891135367</v>
       </c>
@@ -11390,9 +11318,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11538,9 +11463,6 @@
       <c r="O58" t="n">
         <v>52</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.9249807688493514</v>
       </c>
@@ -11934,9 +11856,6 @@
       <c r="O60" t="n">
         <v>17</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.3007258903852361</v>
       </c>
@@ -12330,9 +12249,6 @@
       <c r="O62" t="n">
         <v>91</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>1.721047024489364</v>
       </c>
@@ -12579,7 +12495,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12726,9 +12642,6 @@
       <c r="O64" t="n">
         <v>17</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1588629672808169</v>
       </c>
@@ -13122,9 +13035,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13270,9 +13180,6 @@
       <c r="O67" t="n">
         <v>49</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.8716164937234273</v>
       </c>
@@ -13666,9 +13573,6 @@
       <c r="O69" t="n">
         <v>10</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.1768975825795506</v>
       </c>
@@ -14062,9 +13966,6 @@
       <c r="O71" t="n">
         <v>21</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.1962424889939503</v>
       </c>
@@ -14458,9 +14359,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -14601,16 +14499,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R74" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14763,10 +14658,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -14997,16 +14892,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15159,10 +15051,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15504,7 +15396,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1139</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -14499,13 +14499,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -14499,13 +14499,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -11419,12 +11419,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11458,22 +11458,19 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="O58" t="n">
-        <v>52</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.9249807688493514</v>
+        <v>12</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11493,12 +11490,12 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11506,47 +11503,47 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11578,12 +11575,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11617,29 +11614,29 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="O59" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Yersinia, total</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11649,7 +11646,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -11664,7 +11661,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11699,17 +11696,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+          <t>PHO IDTO current-year monthly preliminary yersiniosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11727,12 +11724,12 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -11740,47 +11737,47 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11812,12 +11809,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -11851,13 +11848,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="O60" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11866,7 +11863,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -11886,12 +11883,12 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -11899,47 +11896,47 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11971,12 +11968,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12010,29 +12007,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="O61" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12057,7 +12054,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12092,17 +12089,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12120,12 +12117,12 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12133,47 +12130,47 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12202,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12244,13 +12241,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="O62" t="n">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="R62" t="n">
-        <v>1.721047024489364</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12259,7 +12256,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12284,7 +12281,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12297,42 +12294,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12364,12 +12361,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12403,29 +12400,29 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="O63" t="n">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12435,7 +12432,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12450,7 +12447,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12485,17 +12482,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12518,7 +12515,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -12531,42 +12528,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12598,12 +12595,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12637,13 +12634,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="O64" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1588629672808169</v>
+        <v>1.721047024489364</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12652,7 +12649,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -12677,7 +12674,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -12690,42 +12687,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12754,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12796,29 +12793,29 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="O65" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -12828,7 +12825,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -12843,7 +12840,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -12878,17 +12875,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -12911,7 +12908,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -12924,42 +12921,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12988,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13021,90 +13018,104 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.1588629672808169</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13131,17 +13142,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13166,31 +13177,48 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="O67" t="n">
-        <v>49</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.8716164937234273</v>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -13198,6 +13226,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -13210,12 +13296,12 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -13223,47 +13309,47 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13290,17 +13376,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13334,170 +13420,81 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>49</v>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13529,12 +13526,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -13568,13 +13565,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O69" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="R69" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.8716164937234273</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -13583,7 +13580,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -13603,12 +13600,12 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -13616,47 +13613,47 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13688,12 +13685,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13727,29 +13724,29 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -13774,7 +13771,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -13809,17 +13806,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13837,12 +13834,12 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -13850,47 +13847,47 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13922,12 +13919,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -13961,13 +13958,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="O71" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1962424889939503</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -13976,7 +13973,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -14001,7 +13998,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -14014,42 +14011,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14081,12 +14078,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14120,29 +14117,29 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="O72" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -14167,7 +14164,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -14202,17 +14199,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14235,7 +14232,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -14248,42 +14245,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14315,12 +14312,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14345,90 +14342,104 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>0.1962424889939503</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14455,17 +14466,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14490,31 +14501,48 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O74" t="n">
-        <v>10</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.1778809170864138</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>21</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -14522,6 +14550,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14534,12 +14620,12 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -14547,47 +14633,47 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14614,17 +14700,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14658,170 +14744,81 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>10</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP75" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV75" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14853,12 +14850,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14892,13 +14889,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R76" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -14907,7 +14904,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -14927,12 +14924,12 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -14940,47 +14937,47 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15012,12 +15009,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15051,29 +15048,29 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -15098,7 +15095,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -15133,17 +15130,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15161,12 +15158,12 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -15174,45 +15171,438 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV77" t="inlineStr">
+      <c r="AV78" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW77" t="inlineStr">
+      <c r="AW78" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr">
+      <c r="AY78" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA77" t="inlineStr">
+      <c r="BA78" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB77" t="inlineStr">
+      <c r="BB78" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC77" t="inlineStr">
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -15334,7 +15724,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -15344,7 +15734,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -15364,7 +15754,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -15396,7 +15786,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1146</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -14889,13 +14889,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1160</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -14889,13 +14889,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O76" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O77" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15282,13 +15282,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15441,10 +15441,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1163</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -14889,13 +14889,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O76" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15048,10 +15048,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O77" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -13958,13 +13958,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -14312,12 +14312,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14351,13 +14351,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="O73" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="R73" t="n">
-        <v>0.1962424889939503</v>
+        <v>1.494095768512745</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -14404,42 +14404,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14471,12 +14471,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14510,29 +14510,29 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="O74" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -14592,17 +14592,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -14638,42 +14638,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14705,12 +14705,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -14735,90 +14735,104 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14845,17 +14859,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14880,31 +14894,48 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O76" t="n">
-        <v>18</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.3201856507555447</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>20</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -14912,6 +14943,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14924,12 +15013,12 @@
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT76" t="n">
@@ -14937,47 +15026,47 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15004,17 +15093,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15048,170 +15137,81 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>18</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV77" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15243,12 +15243,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -15282,13 +15282,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="R78" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT78" t="n">
@@ -15330,47 +15330,47 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15402,12 +15402,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -15441,29 +15441,29 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -15523,17 +15523,17 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15551,12 +15551,12 @@
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT79" t="n">
@@ -15564,45 +15564,438 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV79" t="inlineStr">
+      <c r="AV80" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW79" t="inlineStr">
+      <c r="AW80" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr">
+      <c r="AY80" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA79" t="inlineStr">
+      <c r="BA80" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB79" t="inlineStr">
+      <c r="BB80" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC79" t="inlineStr">
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -15724,7 +16117,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -15734,7 +16127,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -15754,7 +16147,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -15786,7 +16179,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1170</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1336,17 +1336,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1562,7 +1567,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1570,17 +1575,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1721,7 +1731,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1729,17 +1739,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1955,7 +1970,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1963,17 +1978,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2510,7 +2530,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2518,17 +2538,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2744,7 +2769,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2752,17 +2777,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3441,7 +3471,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3449,17 +3479,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3683,17 +3718,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3834,7 +3874,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3842,17 +3882,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4068,7 +4113,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4076,17 +4121,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4623,7 +4673,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4631,17 +4681,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4857,7 +4912,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4865,17 +4920,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5554,7 +5614,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5562,17 +5622,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5788,7 +5853,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5796,17 +5861,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5947,7 +6017,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5955,17 +6025,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6181,7 +6256,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6189,17 +6264,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6736,7 +6816,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6744,17 +6824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6970,7 +7055,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6978,17 +7063,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7664,7 +7754,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7672,17 +7762,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7898,7 +7993,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7906,17 +8001,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8057,7 +8157,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8065,17 +8165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8291,7 +8396,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8299,17 +8404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8843,7 +8953,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8851,17 +8961,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9077,7 +9192,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9085,17 +9200,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9771,7 +9891,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9779,17 +9899,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10005,7 +10130,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10013,17 +10138,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10164,7 +10294,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10172,17 +10302,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10398,7 +10533,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10406,17 +10541,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10950,7 +11090,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -10958,17 +11098,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11184,7 +11329,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11192,17 +11337,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11878,7 +12028,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -11886,17 +12036,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12112,7 +12267,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12120,17 +12275,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12271,7 +12431,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12279,17 +12439,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12505,7 +12670,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12513,17 +12678,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -13057,7 +13227,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13065,17 +13235,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13291,7 +13466,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13299,17 +13474,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13595,7 +13775,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13603,17 +13783,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -13829,7 +14014,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -13837,17 +14022,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -13988,7 +14178,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -13996,17 +14186,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14222,7 +14417,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14230,17 +14425,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14774,7 +14974,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -14782,17 +14982,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -15008,7 +15213,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15016,17 +15221,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -15312,7 +15522,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -15320,17 +15530,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15546,7 +15761,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -15554,17 +15769,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -15705,7 +15925,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -15713,17 +15933,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -15939,7 +16164,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -15947,17 +16172,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -11569,12 +11569,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11608,67 +11608,53 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -11678,17 +11664,17 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -11720,17 +11706,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11764,145 +11750,53 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>12</v>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Yersiniosis</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary yersiniosis notifications; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP59" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV59" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -11912,17 +11806,17 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -11959,12 +11853,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -11998,100 +11892,78 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>52</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.9249807688493514</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12118,17 +11990,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12162,175 +12034,78 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>52</v>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP61" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT61" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV61" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12362,12 +12137,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12401,100 +12176,78 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>17</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.3007258903852361</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12274,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12565,175 +12318,78 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>17</v>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Yersiniose</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP63" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV63" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12765,12 +12421,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12804,95 +12460,78 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>91</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.721047024489364</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12919,17 +12558,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12963,170 +12602,78 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>91</v>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Yersiniosis</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP65" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV65" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13158,12 +12705,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13197,22 +12744,19 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O66" t="n">
-        <v>17</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.1588629672808169</v>
+        <v>12</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13227,7 +12771,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13235,62 +12779,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13322,12 +12861,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13361,29 +12900,29 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O67" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -13393,7 +12932,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -13408,7 +12947,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -13443,17 +12982,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>PHO IDTO current-year monthly preliminary yersiniosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13466,7 +13005,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13474,62 +13013,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13561,12 +13095,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13591,90 +13125,109 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>0.9249807688493514</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13701,7 +13254,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13736,37 +13289,112 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O69" t="n">
-        <v>49</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.8716164937234273</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>52</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -13865,17 +13493,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13900,48 +13528,31 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="O70" t="n">
-        <v>49</v>
+        <v>17</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.3007258903852361</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -13949,64 +13560,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN70" t="b">
-        <v>1</v>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14019,7 +13572,7 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
@@ -14029,7 +13582,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -14037,47 +13590,47 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14104,7 +13657,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14139,37 +13692,112 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O71" t="n">
-        <v>11</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.1945873408375057</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -14268,17 +13896,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14303,48 +13931,31 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="O72" t="n">
-        <v>11</v>
+        <v>91</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.721047024489364</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Yersiniose</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -14352,135 +13963,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN72" t="b">
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
         <v>1</v>
       </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT72" t="n">
-        <v>2</v>
-      </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14055,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14542,37 +14090,112 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="O73" t="n">
-        <v>79</v>
-      </c>
-      <c r="R73" t="n">
-        <v>1.494095768512745</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>91</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -14666,17 +14289,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14701,48 +14324,31 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="O74" t="n">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.1588629672808169</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Yersiniosis</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -14750,64 +14356,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>1</v>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14815,7 +14363,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -14823,57 +14371,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14453,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14935,37 +14488,112 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O75" t="n">
-        <v>20</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0.1868976085656669</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -15064,17 +14692,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -15108,175 +14736,81 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>20</v>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Yersiniainfektion</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP76" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
-        </is>
-      </c>
-      <c r="AT76" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV76" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15308,12 +14842,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15338,12 +14872,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -15352,12 +14886,9 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -15391,12 +14922,12 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -15411,12 +14942,12 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -15453,12 +14984,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -15483,109 +15014,87 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>25</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.4447022927160344</v>
+        <v>0</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15612,17 +15121,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -15647,184 +15156,87 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>25</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV79" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15856,12 +15268,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15886,109 +15298,87 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.05306927477386519</v>
+        <v>0</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16015,217 +15405,5186 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>49</v>
+      </c>
+      <c r="O85" t="n">
+        <v>49</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.8716164937234273</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>49</v>
+      </c>
+      <c r="O86" t="n">
+        <v>49</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>D155</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Yersiniosis</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>耶尔森菌病</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>11</v>
+      </c>
+      <c r="O87" t="n">
+        <v>11</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>11</v>
+      </c>
+      <c r="O88" t="n">
+        <v>11</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>79</v>
+      </c>
+      <c r="O89" t="n">
+        <v>79</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1.494095768512745</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>79</v>
+      </c>
+      <c r="O90" t="n">
+        <v>79</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>20</v>
+      </c>
+      <c r="O91" t="n">
+        <v>20</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.1868976085656669</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>20</v>
+      </c>
+      <c r="O92" t="n">
+        <v>20</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N81" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" t="n">
-        <v>3</v>
-      </c>
-      <c r="U81" t="inlineStr">
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>31</v>
+      </c>
+      <c r="O102" t="n">
+        <v>31</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.5514308429678827</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>31</v>
+      </c>
+      <c r="O103" t="n">
+        <v>31</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>6</v>
+      </c>
+      <c r="O104" t="n">
+        <v>6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>6</v>
+      </c>
+      <c r="O105" t="n">
+        <v>6</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>Yersiniose</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AB105" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
+      <c r="AC105" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD81" t="inlineStr">
+      <c r="AD105" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE81" t="inlineStr">
+      <c r="AE105" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr">
+      <c r="AF105" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG81" t="inlineStr">
+      <c r="AG105" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH81" t="inlineStr">
+      <c r="AH105" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI81" t="inlineStr">
+      <c r="AI105" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AJ105" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK81" t="inlineStr">
+      <c r="AK105" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AM105" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN81" t="b">
+      <c r="AN105" t="b">
         <v>1</v>
       </c>
-      <c r="AO81" t="inlineStr">
+      <c r="AO105" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP81" t="inlineStr">
+      <c r="AP105" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ81" t="inlineStr">
+      <c r="AQ105" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR81" t="inlineStr">
+      <c r="AR105" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
+      <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
-      <c r="AT81" t="n">
+      <c r="AT105" t="n">
         <v>2</v>
       </c>
-      <c r="AU81" t="inlineStr">
+      <c r="AU105" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV81" t="inlineStr">
+      <c r="AV105" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW81" t="inlineStr">
+      <c r="AW105" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX105" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr">
+      <c r="AY105" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
+      <c r="AZ105" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA81" t="inlineStr">
+      <c r="BA105" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB81" t="inlineStr">
+      <c r="BB105" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC81" t="inlineStr">
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -16264,7 +20623,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -16347,7 +20706,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -16357,7 +20716,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -16377,7 +20736,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -16409,7 +20768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1256</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -18900,13 +18900,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O102" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R102" t="n">
-        <v>0.5514308429678827</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -19064,10 +19064,10 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O103" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -19851,13 +19851,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -20015,10 +20015,10 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1266</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="16">
